--- a/data/trans_dic/IP31KM07_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,66; 98,37</t>
+          <t>89,84; 98,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,78; 97,23</t>
+          <t>87,7; 98,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,07; 96,71</t>
+          <t>90,49; 97,14</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,63; 79,68</t>
+          <t>65,43; 85,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,7; 85,7</t>
+          <t>68,33; 83,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,03; 79,68</t>
+          <t>70,34; 83,25</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,68; 95,19</t>
+          <t>86,56; 97,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,62; 96,83</t>
+          <t>83,39; 95,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,57; 95,38</t>
+          <t>87,51; 95,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,53; 88,29</t>
+          <t>59,59; 84,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,85; 84,35</t>
+          <t>73,53; 90,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,21; 84,65</t>
+          <t>70,42; 84,99</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91,87; 100,0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>92,22; 100,0</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,46; 100,0</t>
+          <t>95,8; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,1; 98,78</t>
+          <t>93,82; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,99; 100,0</t>
+          <t>88,06; 98,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,08; 99,36</t>
+          <t>92,86; 99,34</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,55; 96,0</t>
+          <t>72,77; 88,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,1; 86,88</t>
+          <t>87,4; 95,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,28; 89,66</t>
+          <t>80,99; 90,02</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>92,95; 98,75</t>
+          <t>91,41; 98,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,1; 98,11</t>
+          <t>92,53; 98,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,78; 97,88</t>
+          <t>93,54; 97,83</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73,71; 91,28</t>
+          <t>84,85; 90,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83,68; 89,68</t>
+          <t>88,14; 92,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>80,77; 89,15</t>
+          <t>87,15; 90,82</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67900</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69039</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136939</t>
+          <t>109273</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63304; 70234</t>
+          <t>54141; 59088</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60266; 72542</t>
+          <t>48165; 53919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127134; 141206</t>
+          <t>104228; 111896</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76492</t>
+          <t>89679</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97880</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174372</t>
+          <t>166594</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30943; 100119</t>
+          <t>75211; 97900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84323; 108340</t>
+          <t>67878; 83247</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118543; 200851</t>
+          <t>150735; 178382</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>53479</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>49085</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110623</t>
+          <t>102564</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45933; 52879</t>
+          <t>49598; 55961</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55988; 62585</t>
+          <t>45126; 51795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105251; 114635</t>
+          <t>97496; 106399</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>56912</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111786</t>
+          <t>109427</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49846; 61521</t>
+          <t>41602; 59226</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44350; 63569</t>
+          <t>51812; 63485</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100386; 122778</t>
+          <t>98777; 119220</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>74319</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36362; 39579</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>37553; 40719</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71520; 74919</t>
+          <t>71800; 74949</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>53162</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95591</t>
+          <t>88890</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39018; 43749</t>
+          <t>44293; 47209</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50547; 53782</t>
+          <t>38997; 43714</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92265; 97448</t>
+          <t>84964; 90891</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>161</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>114351</t>
+          <t>115411</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>124694</t>
+          <t>112030</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239045</t>
+          <t>227442</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>108294; 118743</t>
+          <t>102288; 124164</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107140; 134707</t>
+          <t>106472; 116506</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>218187; 249918</t>
+          <t>212509; 236212</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>124270</t>
+          <t>150751</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>133038</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>272152</t>
+          <t>283789</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>119592; 127051</t>
+          <t>143634; 154043</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>141986; 151242</t>
+          <t>127596; 135759</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>265234; 276830</t>
+          <t>275982; 288641</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>830</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>566831</t>
+          <t>603352</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558945</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1214801</t>
+          <t>1162296</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>481405; 596171</t>
+          <t>582763; 619772</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>623159; 667911</t>
+          <t>544874; 570790</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1129051; 1246222</t>
+          <t>1137367; 1185217</t>
         </is>
       </c>
     </row>
